--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -912,13 +912,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1608,13 +1608,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|無</t>
+          <t xml:space="preserve">潢|–|無</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 無</t>
         </is>
       </c>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2695,7 +2695,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2942,7 +2942,7 @@
       <c r="F8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 無</t>
         </is>
       </c>
@@ -3152,14 +3152,14 @@
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="K13" s="9"/>

--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2617,586 +2658,586 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">사철가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南
 姑</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아기장</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일년운</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L3" s="17"/>
-      <c r="M3" s="8"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="24"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 潢</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나리</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 潢</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 潢</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="9"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南
 潢</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">중정</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">진달</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 仲</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">열두</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="10"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="27"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흐르러</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 ⁚</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 仲</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">달에</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L6" s="17"/>
-      <c r="M6" s="8"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">미</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사시절</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">종을</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L7" s="17"/>
-      <c r="M7" s="9"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="27"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢
 無</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">들래</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 無</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">정구가</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 潢</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="27"/>
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 潢</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="10"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C9" s="24"/>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲
 姑</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">봄바</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">분명구</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 ⁚</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">종을씨</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 ⁚</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">차</t>
         </is>
       </c>
-      <c r="L9" s="17"/>
-      <c r="M9" s="8"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="24"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="B10" s="23"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="9"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="25"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="B11" s="23"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="27"/>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南
 姑</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="27"/>
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="10"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K11" s="27"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="27"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="B12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E12" s="24"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑
 無</t>
         </is>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="22"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">子</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 潢</t>
         </is>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="8"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="24"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="B13" s="23"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 仲</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="B14" s="23"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="10"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -2639,24 +2639,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       <c r="L3" s="23"/>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
       <c r="L4" s="23"/>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
       <c r="L5" s="23"/>
       <c r="M5" s="27"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       <c r="L6" s="23"/>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       <c r="L7" s="23"/>
       <c r="M7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
       <c r="L8" s="23"/>
       <c r="M8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
       <c r="L9" s="23"/>
       <c r="M9" s="24"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23"/>
       <c r="C10" s="25"/>
@@ -3099,7 +3099,7 @@
       <c r="L10" s="23"/>
       <c r="M10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23"/>
       <c r="C11" s="27"/>
@@ -3133,7 +3133,7 @@
       <c r="L11" s="23"/>
       <c r="M11" s="27"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
       <c r="C12" s="24"/>
@@ -3173,7 +3173,7 @@
       <c r="L12" s="23"/>
       <c r="M12" s="24"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
       <c r="C13" s="25"/>
@@ -3207,7 +3207,7 @@
       <c r="L13" s="23"/>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23"/>
       <c r="C14" s="27"/>

--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -841,13 +841,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|⁚</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-⁚</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1259,13 +1258,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|⁚</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-⁚</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2044,13 +2042,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|⁚</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-⁚</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2862,8 +2859,7 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-⁚</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -3048,8 +3044,7 @@
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-⁚</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I9" s="24" t="inlineStr">
@@ -3059,8 +3054,7 @@
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-⁚</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="K9" s="24" t="inlineStr">

--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -2683,7 +2683,9 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아기장</t>
+          <t xml:space="preserve">아
+기
+장</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -2703,7 +2705,9 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">일년운</t>
+          <t xml:space="preserve">일
+년
+운</t>
         </is>
       </c>
       <c r="H3" s="23" t="inlineStr">
@@ -2747,7 +2751,8 @@
       </c>
       <c r="E4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">나리</t>
+          <t xml:space="preserve">나
+리</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
@@ -2795,7 +2800,8 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">중정</t>
+          <t xml:space="preserve">중
+정</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -2806,7 +2812,8 @@
       </c>
       <c r="E5" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">진달</t>
+          <t xml:space="preserve">진
+달</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -2818,7 +2825,8 @@
       </c>
       <c r="G5" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">열두</t>
+          <t xml:space="preserve">열
+두</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
@@ -2854,7 +2862,9 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">흐르러</t>
+          <t xml:space="preserve">흐
+르
+러</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -2876,7 +2886,8 @@
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">달에</t>
+          <t xml:space="preserve">달
+에</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -2929,7 +2940,9 @@
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">사시절</t>
+          <t xml:space="preserve">사
+시
+절</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
@@ -2939,7 +2952,8 @@
       </c>
       <c r="I7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">종을</t>
+          <t xml:space="preserve">종
+을</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -2973,7 +2987,8 @@
       </c>
       <c r="E8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">들래</t>
+          <t xml:space="preserve">들
+래</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -2985,7 +3000,9 @@
       </c>
       <c r="G8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">정구가</t>
+          <t xml:space="preserve">정
+구
+가</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -3028,7 +3045,8 @@
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">봄바</t>
+          <t xml:space="preserve">봄
+바</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -3039,7 +3057,9 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">분명구</t>
+          <t xml:space="preserve">분
+명
+구</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -3049,7 +3069,9 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">종을씨</t>
+          <t xml:space="preserve">종
+을
+씨</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">

--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,6 +239,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2681,7 +2704,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 기
@@ -2693,7 +2716,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -2703,7 +2726,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">일
 년
@@ -2715,7 +2738,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
@@ -2725,13 +2748,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
       <c r="L3" s="23"/>
-      <c r="M3" s="24"/>
+      <c r="M3" s="30"/>
     </row>
     <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
@@ -2741,7 +2764,7 @@
 △</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
@@ -2749,7 +2772,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 리</t>
@@ -2761,7 +2784,7 @@
 △</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
@@ -2769,7 +2792,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -2781,13 +2804,13 @@
 潢</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="L4" s="23"/>
-      <c r="M4" s="25"/>
+      <c r="M4" s="31"/>
     </row>
     <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
@@ -2798,7 +2821,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">중
 정</t>
@@ -2810,7 +2833,7 @@
 南</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">진
 달</t>
@@ -2823,7 +2846,7 @@
 仲</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">열
 두</t>
@@ -2834,7 +2857,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
@@ -2844,13 +2867,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
       <c r="L5" s="23"/>
-      <c r="M5" s="27"/>
+      <c r="M5" s="33"/>
     </row>
     <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
@@ -2860,7 +2883,7 @@
 無</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흐
 르
@@ -2872,7 +2895,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
@@ -2884,7 +2907,7 @@
 仲</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">달
 에</t>
@@ -2895,7 +2918,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -2906,13 +2929,13 @@
 潢</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="L6" s="23"/>
-      <c r="M6" s="24"/>
+      <c r="M6" s="30"/>
     </row>
     <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
@@ -2921,13 +2944,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">미</t>
         </is>
@@ -2938,7 +2961,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">사
 시
@@ -2950,7 +2973,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">종
 을</t>
@@ -2961,13 +2984,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="K7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
       <c r="L7" s="23"/>
-      <c r="M7" s="25"/>
+      <c r="M7" s="31"/>
     </row>
     <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
@@ -2977,7 +3000,7 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
@@ -2985,7 +3008,7 @@
 無</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">들
 래</t>
@@ -2998,7 +3021,7 @@
 無</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">정
 구
@@ -3012,7 +3035,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I8" s="27"/>
+      <c r="I8" s="33"/>
       <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
@@ -3020,13 +3043,13 @@
 潢</t>
         </is>
       </c>
-      <c r="K8" s="27" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="L8" s="23"/>
-      <c r="M8" s="27"/>
+      <c r="M8" s="33"/>
     </row>
     <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
@@ -3035,7 +3058,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="24"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
@@ -3043,7 +3066,7 @@
 姑</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">봄
 바</t>
@@ -3055,7 +3078,7 @@
 仲</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">분
 명
@@ -3067,7 +3090,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">종
 을
@@ -3079,53 +3102,53 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K9" s="24" t="inlineStr">
+      <c r="K9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">차</t>
         </is>
       </c>
       <c r="L9" s="23"/>
-      <c r="M9" s="24"/>
+      <c r="M9" s="30"/>
     </row>
     <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="25"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="25"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="H10" s="23"/>
-      <c r="I10" s="25"/>
+      <c r="I10" s="31"/>
       <c r="J10" s="23"/>
-      <c r="K10" s="25"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="23"/>
-      <c r="M10" s="25"/>
+      <c r="M10" s="31"/>
     </row>
     <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23"/>
-      <c r="C11" s="27"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="27"/>
+      <c r="E11" s="33"/>
       <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
@@ -3133,32 +3156,32 @@
 姑</t>
         </is>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K11" s="27"/>
+      <c r="K11" s="33"/>
       <c r="L11" s="23"/>
-      <c r="M11" s="27"/>
+      <c r="M11" s="33"/>
     </row>
     <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="24"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
@@ -3166,14 +3189,14 @@
 無</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">子</t>
         </is>
@@ -3185,20 +3208,20 @@
 潢</t>
         </is>
       </c>
-      <c r="K12" s="24"/>
+      <c r="K12" s="30"/>
       <c r="L12" s="23"/>
-      <c r="M12" s="24"/>
+      <c r="M12" s="30"/>
     </row>
     <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
@@ -3206,54 +3229,54 @@
 仲</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="23"/>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
     </row>
     <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23"/>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="23"/>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,12 +212,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -232,31 +221,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -329,7 +306,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4 / 12정간</t>
+          <t xml:space="preserve">4/4 / 8정간</t>
         </is>
       </c>
     </row>
@@ -353,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
     </row>
@@ -365,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -429,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">우측 여백 "경기민요 "사철가"" "굿거리". 12정간, 굵은 선 3칸마다. 오른쪽 1줄은 비어 있고(도입 전 빈 줄) 7·8줄도 비어 실제 내용은 2~6줄. 상단 2~4줄에 "후렴" 표시와 이음줄(슬러). 율명 옆·칸 내 작은 물결선(요성)과 반복 흘림은 기호표에 없어 생략하고 해당 칸 비고에 적음. 하단 양식번호 "196"은 무시. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식(번호 1~16)이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명이 2~3개씩 쌓인 굿거리 → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 1은 비어 있어 인쇄 열 2를 줄1로, 인쇄 열 2~6 = 줄1~5, 인쇄 열 7·8은 비어 제외. 위쪽 인쇄 열 2~4에 '후렴' 표시와 괄호선(줄1~3 = 후렴 '지화자 좋네…'). 우측 여백 '경기민요 "사철가" "굿거리"'. 가사는 각 율명 줄 오른쪽 칸. 하단 196 무시.</t>
         </is>
       </c>
     </row>
@@ -604,10 +581,10 @@
         </is>
       </c>
       <c r="C2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -617,12 +594,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–|·</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–
+·</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -643,10 +622,10 @@
         </is>
       </c>
       <c r="C3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2">
         <v>2</v>
@@ -654,28 +633,24 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無|姑|潢</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–南|潢無</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-姑
-潢</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+–南
+潢無</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래쪽 氵계열 겹쳐 潢으로 봄</t>
-        </is>
-      </c>
+      <c r="J3" s="4"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4">
@@ -688,10 +663,10 @@
         </is>
       </c>
       <c r="C4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2">
         <v>3</v>
@@ -701,12 +676,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–|·</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–
+·</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -727,34 +704,39 @@
         </is>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2">
         <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無|潢</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–|潢無</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+–
+潢無</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="J5" s="4"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無 오른쪽 작은 두 점</t>
+        </is>
+      </c>
       <c r="K5" s="2"/>
     </row>
     <row r="6">
@@ -767,10 +749,10 @@
         </is>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
@@ -778,26 +760,24 @@
       <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|–|–</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+–</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종을(가사)</t>
-        </is>
-      </c>
+      <c r="J6" s="4"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7">
@@ -810,10 +790,10 @@
         </is>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
@@ -823,13 +803,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑|潢</t>
+          <t xml:space="preserve">無|–南|潢</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-姑
+–南
 潢</t>
         </is>
       </c>
@@ -851,30 +831,32 @@
         </is>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
         <v>7</v>
       </c>
       <c r="F8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">無|–|–</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">無
+–
+–</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">차</t>
+          <t xml:space="preserve">자</t>
         </is>
       </c>
       <c r="J8" s="4"/>
@@ -890,25 +872,27 @@
         </is>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–|–|潢無</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–
+–
+潢無</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -931,24 +915,28 @@
         <v>2</v>
       </c>
       <c r="E10" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑|潢</t>
+          <t xml:space="preserve">南|–|·</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-姑
-潢</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
+          <t xml:space="preserve">南
+–
+·</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
       <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
@@ -968,23 +956,28 @@
         <v>2</v>
       </c>
       <c r="E11" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|–</t>
+          <t xml:space="preserve">無|–南|潢無</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
+          <t xml:space="preserve">無
+–南
+潢無</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
       <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
@@ -1004,23 +997,28 @@
         <v>2</v>
       </c>
       <c r="E12" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">南|–|·</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
+          <t xml:space="preserve">南
+–
+·</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
       <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
@@ -1034,30 +1032,32 @@
         </is>
       </c>
       <c r="C13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">無|·|△</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">無
+·
+△</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">종</t>
+          <t xml:space="preserve">네</t>
         </is>
       </c>
       <c r="J13" s="4"/>
@@ -1073,32 +1073,32 @@
         </is>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑|潢</t>
+          <t xml:space="preserve">潢|–|潢</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-姑
+          <t xml:space="preserve">潢
+–
 潢</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">좋을</t>
         </is>
       </c>
       <c r="J14" s="4"/>
@@ -1114,30 +1114,32 @@
         </is>
       </c>
       <c r="C15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢|–潢|無潢</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢
+–潢
+無潢</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">종</t>
+          <t xml:space="preserve">좋을씨</t>
         </is>
       </c>
       <c r="J15" s="4"/>
@@ -1153,30 +1155,32 @@
         </is>
       </c>
       <c r="C16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F16" s="2">
         <v>2</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">㴌|–|㳞㴌</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">㴌
+–
+㳞㴌</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">구</t>
         </is>
       </c>
       <c r="J16" s="4"/>
@@ -1192,30 +1196,32 @@
         </is>
       </c>
       <c r="C17" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" s="2">
         <v>2</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|無南|仲</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+無南
+仲</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">종을</t>
+          <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="J17" s="4"/>
@@ -1237,24 +1243,28 @@
         <v>3</v>
       </c>
       <c r="E18" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑|潢</t>
+          <t xml:space="preserve">姑|姑|姑</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
+          <t xml:space="preserve">姑
 姑
-潢</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
+姑</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일년은</t>
+        </is>
+      </c>
       <c r="J18" s="4"/>
       <c r="K18" s="2"/>
     </row>
@@ -1274,26 +1284,24 @@
         <v>3</v>
       </c>
       <c r="E19" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종을씨</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+–
+△</t>
+        </is>
+      </c>
+      <c r="I19" s="2"/>
       <c r="J19" s="4"/>
       <c r="K19" s="2"/>
     </row>
@@ -1313,22 +1321,28 @@
         <v>3</v>
       </c>
       <c r="E20" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F20" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南|無南|仲姑</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I20" s="2"/>
+          <t xml:space="preserve">南
+無南
+仲姑</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">열두</t>
+        </is>
+      </c>
       <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
@@ -1348,25 +1362,26 @@
         <v>3</v>
       </c>
       <c r="E21" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">南|無南|仲姑</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-無</t>
+          <t xml:space="preserve">南
+無南
+仲姑</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">子</t>
+          <t xml:space="preserve">달에</t>
         </is>
       </c>
       <c r="J21" s="4"/>
@@ -1388,22 +1403,28 @@
         <v>3</v>
       </c>
       <c r="E22" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">南|南|南</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I22" s="2"/>
+          <t xml:space="preserve">南
+南
+南</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사시절</t>
+        </is>
+      </c>
       <c r="J22" s="4"/>
       <c r="K22" s="2"/>
     </row>
@@ -1423,23 +1444,33 @@
         <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F23" s="2">
-        <v>4</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|–㴌|潢無</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–㴌
+潢無</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">절구가</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 순서 사시절/절구가 그대로</t>
+        </is>
+      </c>
       <c r="K23" s="2"/>
     </row>
     <row r="24">
@@ -1452,37 +1483,35 @@
         </is>
       </c>
       <c r="C24" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일년운</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">州 모양 반복(요성·반복 흘림)</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無南|仲姑</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無南
+仲姑</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분명구</t>
+        </is>
+      </c>
+      <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
     <row r="25">
@@ -1495,29 +1524,34 @@
         </is>
       </c>
       <c r="C25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|△</t>
+          <t xml:space="preserve">南|–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">南
+–
 △</t>
         </is>
       </c>
-      <c r="I25" s="2"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="J25" s="4"/>
       <c r="K25" s="2"/>
     </row>
@@ -1537,33 +1571,29 @@
         <v>4</v>
       </c>
       <c r="E26" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2">
         <v>1</v>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|無|仲</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無
-仲</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">열두</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 仲 확실치 않음</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|–|·</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+·</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개</t>
+        </is>
+      </c>
+      <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
     <row r="27">
@@ -1582,26 +1612,26 @@
         <v>4</v>
       </c>
       <c r="E27" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無|仲</t>
+          <t xml:space="preserve">無|–南|潢無</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-無
-仲</t>
+          <t xml:space="preserve">無
+–南
+潢無</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">달에</t>
+          <t xml:space="preserve">나리</t>
         </is>
       </c>
       <c r="J27" s="4"/>
@@ -1623,25 +1653,25 @@
         <v>4</v>
       </c>
       <c r="E28" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢</t>
+          <t xml:space="preserve">南|–南</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢</t>
+          <t xml:space="preserve">南
+–南</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사시절</t>
+          <t xml:space="preserve">진달</t>
         </is>
       </c>
       <c r="J28" s="4"/>
@@ -1663,26 +1693,26 @@
         <v>4</v>
       </c>
       <c r="E29" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–|無</t>
+          <t xml:space="preserve">無|–|△</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-–
-無</t>
+          <t xml:space="preserve">無
+–
+△</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정구가</t>
+          <t xml:space="preserve">래</t>
         </is>
       </c>
       <c r="J29" s="4"/>
@@ -1704,30 +1734,31 @@
         <v>4</v>
       </c>
       <c r="E30" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|仲</t>
+          <t xml:space="preserve">潢|–|·</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-仲</t>
+–
+·</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">분명구</t>
+          <t xml:space="preserve">미</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래 仲? 확실치 않음</t>
+          <t xml:space="preserve">가사 미/민?</t>
         </is>
       </c>
       <c r="K30" s="2"/>
@@ -1748,25 +1779,26 @@
         <v>4</v>
       </c>
       <c r="E31" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無</t>
+          <t xml:space="preserve">潢|–無|潢無</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-無</t>
+          <t xml:space="preserve">潢
+–無
+潢無</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나</t>
+          <t xml:space="preserve">들래</t>
         </is>
       </c>
       <c r="J31" s="4"/>
@@ -1788,24 +1820,28 @@
         <v>4</v>
       </c>
       <c r="E32" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|南|姑</t>
+          <t xml:space="preserve">南|仲姑|㑖</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-南
-姑</t>
-        </is>
-      </c>
-      <c r="I32" s="2"/>
+仲姑
+㑖</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄바</t>
+        </is>
+      </c>
       <c r="J32" s="4"/>
       <c r="K32" s="2"/>
     </row>
@@ -1825,27 +1861,31 @@
         <v>4</v>
       </c>
       <c r="E33" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F33" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|姑|無</t>
+          <t xml:space="preserve">姑|仲姑|潢㒇</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-姑
-無</t>
-        </is>
-      </c>
-      <c r="I33" s="3"/>
+          <t xml:space="preserve">姑
+仲姑
+潢㒇</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">람에</t>
+        </is>
+      </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래 겹쳐 씀</t>
+          <t xml:space="preserve">아래 潢㒇: 無에 亻 붙어 보임</t>
         </is>
       </c>
       <c r="K33" s="2"/>
@@ -1860,30 +1900,34 @@
         </is>
       </c>
       <c r="C34" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無|仲</t>
+          <t xml:space="preserve">姑|姑|姑</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-無
-仲</t>
-        </is>
-      </c>
-      <c r="I34" s="2"/>
+          <t xml:space="preserve">姑
+姑
+姑</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아기장</t>
+        </is>
+      </c>
       <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
@@ -1897,25 +1941,27 @@
         </is>
       </c>
       <c r="C35" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–
+–
+△</t>
         </is>
       </c>
       <c r="I35" s="2"/>
@@ -1938,27 +1984,33 @@
         <v>5</v>
       </c>
       <c r="E36" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2">
         <v>1</v>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개</t>
-        </is>
-      </c>
-      <c r="J36" s="4"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無南|潢無</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無南
+潢無</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥청</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 흥청/충청?</t>
+        </is>
+      </c>
       <c r="K36" s="2"/>
     </row>
     <row r="37">
@@ -1977,29 +2029,33 @@
         <v>5</v>
       </c>
       <c r="E37" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2">
         <v>1</v>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無|姑|潢</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-姑
-潢</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나리</t>
-        </is>
-      </c>
-      <c r="J37" s="4"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無南|仲姑</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無南
+仲姑</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흐드러져</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 흐드/흐르?</t>
+        </is>
+      </c>
       <c r="K37" s="2"/>
     </row>
     <row r="38">
@@ -2018,25 +2074,26 @@
         <v>5</v>
       </c>
       <c r="E38" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|南</t>
+          <t xml:space="preserve">南|南|–</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-南</t>
+南
+–</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">진달</t>
+          <t xml:space="preserve">흔들</t>
         </is>
       </c>
       <c r="J38" s="4"/>
@@ -2058,24 +2115,26 @@
         <v>5</v>
       </c>
       <c r="E39" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F39" s="2">
         <v>2</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">姑|–㴌|潢無</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">姑
+–㴌
+潢無</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">래</t>
+          <t xml:space="preserve">거리고</t>
         </is>
       </c>
       <c r="J39" s="4"/>
@@ -2097,24 +2156,26 @@
         <v>5</v>
       </c>
       <c r="E40" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F40" s="2">
         <v>2</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南|無南|仲姑</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南
+無南
+仲姑</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미</t>
+          <t xml:space="preserve">피어난</t>
         </is>
       </c>
       <c r="J40" s="4"/>
@@ -2136,522 +2197,33 @@
         <v>5</v>
       </c>
       <c r="E41" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F41" s="2">
         <v>2</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|潢|無</t>
+          <t xml:space="preserve">南|–|△</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-潢
-無</t>
+          <t xml:space="preserve">南
+–
+△</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">들래</t>
+          <t xml:space="preserve">다</t>
         </is>
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42">
-      <c r="A42" s="2">
-        <v>1</v>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C42" s="2">
-        <v>5</v>
-      </c>
-      <c r="D42" s="2">
-        <v>5</v>
-      </c>
-      <c r="E42" s="2">
-        <v>7</v>
-      </c>
-      <c r="F42" s="2">
-        <v>3</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|仲|姑</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-仲
-姑</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봄바</t>
-        </is>
-      </c>
-      <c r="J42" s="4"/>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2">
-        <v>1</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C43" s="2">
-        <v>5</v>
-      </c>
-      <c r="D43" s="2">
-        <v>5</v>
-      </c>
-      <c r="E43" s="2">
-        <v>8</v>
-      </c>
-      <c r="F43" s="2">
-        <v>3</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2">
-        <v>1</v>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C44" s="2">
-        <v>5</v>
-      </c>
-      <c r="D44" s="2">
-        <v>5</v>
-      </c>
-      <c r="E44" s="2">
-        <v>9</v>
-      </c>
-      <c r="F44" s="2">
-        <v>3</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I44" s="2"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2">
-        <v>1</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C45" s="2">
-        <v>5</v>
-      </c>
-      <c r="D45" s="2">
-        <v>5</v>
-      </c>
-      <c r="E45" s="2">
-        <v>10</v>
-      </c>
-      <c r="F45" s="2">
-        <v>4</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I45" s="2"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2">
-        <v>1</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C46" s="2">
-        <v>5</v>
-      </c>
-      <c r="D46" s="2">
-        <v>5</v>
-      </c>
-      <c r="E46" s="2">
-        <v>11</v>
-      </c>
-      <c r="F46" s="2">
-        <v>4</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I46" s="2"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2">
-        <v>1</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C47" s="2">
-        <v>5</v>
-      </c>
-      <c r="D47" s="2">
-        <v>5</v>
-      </c>
-      <c r="E47" s="2">
-        <v>12</v>
-      </c>
-      <c r="F47" s="2">
-        <v>4</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2">
-        <v>1</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C48" s="2">
-        <v>6</v>
-      </c>
-      <c r="D48" s="2">
-        <v>6</v>
-      </c>
-      <c r="E48" s="2">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
-        <v>1</v>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|南|姑</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-南
-姑</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아기장</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">州 모양 반복(요성)</t>
-        </is>
-      </c>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2">
-        <v>1</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C49" s="2">
-        <v>6</v>
-      </c>
-      <c r="D49" s="2">
-        <v>6</v>
-      </c>
-      <c r="E49" s="2">
-        <v>2</v>
-      </c>
-      <c r="F49" s="2">
-        <v>1</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|△</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-△</t>
-        </is>
-      </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2">
-        <v>1</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C50" s="2">
-        <v>6</v>
-      </c>
-      <c r="D50" s="2">
-        <v>6</v>
-      </c>
-      <c r="E50" s="2">
-        <v>3</v>
-      </c>
-      <c r="F50" s="2">
-        <v>1</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|南|潢</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-南
-潢</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중정</t>
-        </is>
-      </c>
-      <c r="J50" s="4"/>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2">
-        <v>1</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C51" s="2">
-        <v>6</v>
-      </c>
-      <c r="D51" s="2">
-        <v>6</v>
-      </c>
-      <c r="E51" s="2">
-        <v>4</v>
-      </c>
-      <c r="F51" s="2">
-        <v>2</v>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|無</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흐르러</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 글자 확실치 않음</t>
-        </is>
-      </c>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2">
-        <v>1</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C52" s="2">
-        <v>6</v>
-      </c>
-      <c r="D52" s="2">
-        <v>6</v>
-      </c>
-      <c r="E52" s="2">
-        <v>5</v>
-      </c>
-      <c r="F52" s="2">
-        <v>2</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I52" s="2"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2">
-        <v>1</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C53" s="2">
-        <v>6</v>
-      </c>
-      <c r="D53" s="2">
-        <v>6</v>
-      </c>
-      <c r="E53" s="2">
-        <v>6</v>
-      </c>
-      <c r="F53" s="2">
-        <v>2</v>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|無</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="I53" s="2"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2">
-        <v>1</v>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
-        </is>
-      </c>
-      <c r="C54" s="2">
-        <v>6</v>
-      </c>
-      <c r="D54" s="2">
-        <v>6</v>
-      </c>
-      <c r="E54" s="2">
-        <v>7</v>
-      </c>
-      <c r="F54" s="2">
-        <v>3</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K54"/>
+  <autoFilter ref="A1:K41"/>
 </worksheet>
 </file>
 
@@ -2669,14 +2241,12 @@
     <col min="9" max="9" width="6" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="82.06" customHeight="1">
+    <row r="2" ht="77.61" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2692,148 +2262,152 @@
       <c r="I2" s="20"/>
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-    </row>
-    <row r="3" ht="82.06" customHeight="1">
+    </row>
+    <row r="3" ht="77.61" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-南
+          <t xml:space="preserve">姑
+姑
 姑</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 기
 장</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+–</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G3" s="29" t="inlineStr">
+          <t xml:space="preserve">姑
+姑
+姑</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일
 년
-운</t>
-        </is>
-      </c>
-      <c r="H3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종</t>
-        </is>
-      </c>
-      <c r="J3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K3" s="30" t="inlineStr">
+은</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+–</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+–</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L3" s="23"/>
-      <c r="M3" s="30"/>
-    </row>
-    <row r="4" ht="82.06" customHeight="1">
+    </row>
+    <row r="4" ht="77.61" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
+–
 △</t>
         </is>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-姑
-潢</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
+–南
+潢無</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 리</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
+–
 △</t>
         </is>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="G4" s="23"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-姑
-潢</t>
-        </is>
-      </c>
-      <c r="I4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
+–南
+潢無</t>
+        </is>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-姑
-潢</t>
-        </is>
-      </c>
-      <c r="K4" s="32" t="inlineStr">
+–南
+潢無</t>
+        </is>
+      </c>
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L4" s="23"/>
-      <c r="M4" s="31"/>
-    </row>
-    <row r="5" ht="82.06" customHeight="1">
+    </row>
+    <row r="5" ht="77.61" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-南
-潢</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중
-정</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-南</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無南
+潢無</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥
+청</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">진
 달</t>
@@ -2842,231 +2416,269 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-無
-仲</t>
-        </is>
-      </c>
-      <c r="G5" s="34" t="inlineStr">
+無南
+仲姑</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">열
 두</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종</t>
-        </is>
-      </c>
-      <c r="J5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K5" s="33" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+–</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+–</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L5" s="23"/>
-      <c r="M5" s="33"/>
-    </row>
-    <row r="6" ht="82.06" customHeight="1">
+    </row>
+    <row r="6" ht="77.61" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無南
+仲姑</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">흐
-르
-러</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E6" s="30" t="inlineStr">
+드
+러
+져</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–
+△</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無
-仲</t>
-        </is>
-      </c>
-      <c r="G6" s="30" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無南
+仲姑</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">달
 에</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
-        </is>
-      </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="K6" s="30" t="inlineStr">
+–
+△</t>
+        </is>
+      </c>
+      <c r="I6" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–
+潢無</t>
+        </is>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L6" s="23"/>
-      <c r="M6" s="30"/>
-    </row>
-    <row r="7" ht="82.06" customHeight="1">
+    </row>
+    <row r="7" ht="77.61" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南
+–</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흔
+들</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–
+–</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">미</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="G7" s="31" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南
+南</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사
 시
 절</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–
+潢</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋
 을</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K7" s="32" t="inlineStr">
+          <t xml:space="preserve">南
+–
+–</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L7" s="23"/>
-      <c r="M7" s="31"/>
-    </row>
-    <row r="8" ht="82.06" customHeight="1">
+    </row>
+    <row r="8" ht="77.61" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-潢
-無</t>
-        </is>
-      </c>
-      <c r="E8" s="33" t="inlineStr">
+–㴌
+潢無</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">거
+리
+고</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–無
+潢無</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">들
 래</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-–
-無</t>
-        </is>
-      </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–㴌
+潢無</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">절
 구
 가</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–潢
+無潢</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋
+을
+씨</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-姑
+–南
 潢</t>
         </is>
       </c>
-      <c r="I8" s="33"/>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-姑
-潢</t>
-        </is>
-      </c>
-      <c r="K8" s="33" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L8" s="23"/>
-      <c r="M8" s="33"/>
-    </row>
-    <row r="9" ht="82.06" customHeight="1">
+    </row>
+    <row r="9" ht="77.61" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-仲
-姑</t>
-        </is>
-      </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無南
+仲姑</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">피
+어
+난</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+仲姑
+㑖</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">봄
 바</t>
@@ -3074,213 +2686,106 @@
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-仲</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="inlineStr">
+          <t xml:space="preserve">南
+無南
+仲姑</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">분
 명
 구</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종
-을
-씨</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">차</t>
-        </is>
-      </c>
-      <c r="L9" s="23"/>
-      <c r="M9" s="30"/>
-    </row>
-    <row r="10" ht="82.06" customHeight="1">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+㳞㴌</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–
+–</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="77.61" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="G10" s="31" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+△</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+仲姑
+潢㒇</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">람
+에</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+△</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H10" s="23"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="31"/>
-    </row>
-    <row r="11" ht="82.06" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-南
-姑</t>
-        </is>
-      </c>
-      <c r="G11" s="33"/>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I11" s="33"/>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K11" s="33"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="33"/>
-    </row>
-    <row r="12" ht="82.06" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-姑
-無</t>
-        </is>
-      </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-姑
-潢</t>
-        </is>
-      </c>
-      <c r="K12" s="30"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="30"/>
-    </row>
-    <row r="13" ht="82.06" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無南
 仲</t>
         </is>
       </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="23" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="31"/>
-    </row>
-    <row r="14" ht="82.06" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G14" s="33"/>
-      <c r="H14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I14" s="33"/>
-      <c r="J14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="K14" s="33"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="33"/>
+–
+潢無</t>
+        </is>
+      </c>
+      <c r="K10" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B2:K2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -406,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식(번호 1~16)이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명이 2~3개씩 쌓인 굿거리 → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 1은 비어 있어 인쇄 열 2를 줄1로, 인쇄 열 2~6 = 줄1~5, 인쇄 열 7·8은 비어 제외. 위쪽 인쇄 열 2~4에 '후렴' 표시와 괄호선(줄1~3 = 후렴 '지화자 좋네…'). 우측 여백 '경기민요 "사철가" "굿거리"'. 가사는 각 율명 줄 오른쪽 칸. 하단 196 무시.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식(번호 1~16)이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명이 2~3개씩 쌓인 굿거리 → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 1은 비어 있어 인쇄 열 2를 줄1로, 인쇄 열 2~6 = 줄1~5, 인쇄 열 7·8은 비어 제외. 위쪽 인쇄 열 2~4에 '후렴' 표시와 괄호선(줄1~3 = 후렴 '지화자 좋네…'). 우측 여백 '경기민요 "사철가" "굿거리"'. 가사는 각 율명 줄 오른쪽 칸. 하단 196 무시. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래 潢㒇: 無에 亻 붙어 보임</t>
+          <t xml:space="preserve">아래 潢㒇: 無에 亻 붙어 보임; 潢/黃?</t>
         </is>
       </c>
       <c r="K33" s="2"/>

--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -2226,6 +2226,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2240,10 +2243,10 @@
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="77.61" customHeight="1">
+    <row r="2" ht="43.48" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2260,7 +2263,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="77.61" customHeight="1">
+    <row r="3" ht="96.85" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2327,7 +2330,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.61" customHeight="1">
+    <row r="4" ht="96.85" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2383,7 +2386,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="77.61" customHeight="1">
+    <row r="5" ht="96.85" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="24" t="inlineStr">
         <is>
@@ -2448,7 +2451,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="77.61" customHeight="1">
+    <row r="6" ht="96.85" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="24" t="inlineStr">
         <is>
@@ -2515,7 +2518,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77.61" customHeight="1">
+    <row r="7" ht="96.85" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2582,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="77.61" customHeight="1">
+    <row r="8" ht="96.85" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2652,7 +2655,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="77.61" customHeight="1">
+    <row r="9" ht="96.85" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2720,7 +2723,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="77.61" customHeight="1">
+    <row r="10" ht="96.85" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2786,6 +2789,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="92"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/사철가 (채보1).xlsx
+++ b/sheets/민요/검수/사철가 (채보1).xlsx
@@ -2231,22 +2231,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="43.48" customHeight="true">
+    <row r="2" ht="42.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="96.85" customHeight="true">
+    <row r="3" ht="93.77" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="96.85" customHeight="true">
+    <row r="4" ht="93.77" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="96.85" customHeight="true">
+    <row r="5" ht="93.77" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="96.85" customHeight="true">
+    <row r="6" ht="93.77" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="24" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="96.85" customHeight="true">
+    <row r="7" ht="93.77" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="96.85" customHeight="true">
+    <row r="8" ht="93.77" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="96.85" customHeight="true">
+    <row r="9" ht="93.77" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="96.85" customHeight="true">
+    <row r="10" ht="93.77" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2789,6 +2789,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="92"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="95"/>
 </worksheet>
 </file>